--- a/input.xlsx
+++ b/input.xlsx
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>序号</t>
   </si>
   <si>
-    <t>单词 / 短语（含音标）</t>
+    <t>单词（含音标）</t>
   </si>
   <si>
     <t>释义</t>
@@ -41,391 +41,364 @@
     <t>例句</t>
   </si>
   <si>
-    <t>violinist [ˌvaɪəˈlɪnɪst]</t>
-  </si>
-  <si>
-    <t>n. 小提琴手;小提琴演奏者</t>
-  </si>
-  <si>
-    <t>The violinist gave an excellent performance. 小提琴家进行了一场精彩的演奏。</t>
-  </si>
-  <si>
-    <t>flashback [ˈflæʃbæk]</t>
-  </si>
-  <si>
-    <t>n. 闪回;倒叙</t>
-  </si>
-  <si>
-    <t>His boyhood is shown in a flashback. 他少年时代是用倒叙法来表现的。</t>
-  </si>
-  <si>
-    <t>glucose [ˈɡluːkəʊs]</t>
-  </si>
-  <si>
-    <t>n. 葡萄糖</t>
-  </si>
-  <si>
-    <t>low level of glucose in the blood 血液中葡萄糖含量低</t>
-  </si>
-  <si>
-    <t>hegemony [hɪˈdʒeməni]</t>
-  </si>
-  <si>
-    <t>n. 霸权;霸权主义</t>
-  </si>
-  <si>
-    <t>political hegemony 政治霸权</t>
-  </si>
-  <si>
-    <t>helium [ˈhiːliəm]</t>
-  </si>
-  <si>
-    <t>n. 氦</t>
-  </si>
-  <si>
-    <t>The element of helium was first found in the sun. 氦元素最初是在太阳里发现的。</t>
-  </si>
-  <si>
-    <t>fully-licensed [ˈfʊliˈlaɪs(ə)nst]</t>
-  </si>
-  <si>
-    <t>adj. 完全获得许可的</t>
-  </si>
-  <si>
-    <t>Our restaurant is fully-licensed. 本餐厅完全获得了经营许可。</t>
-  </si>
-  <si>
-    <t>terrify [ˈterɪfaɪ]</t>
-  </si>
-  <si>
-    <t>v. 使恐惧;使惊吓</t>
-  </si>
-  <si>
-    <t>Rats terrify me. 老鼠使我害怕。</t>
-  </si>
-  <si>
-    <t>reoriented [riˈɔːrientɪd]</t>
-  </si>
-  <si>
-    <t>adj. 重新定位的</t>
-  </si>
-  <si>
-    <t>Agriculture production needs to be reoriented towards regional concentration, quality improvement and industrialization. 农业生产需加快向区域化、优质化、产业化方向发展。</t>
-  </si>
-  <si>
-    <t>rummage [ˈrʌmɪdʒ]</t>
-  </si>
-  <si>
-    <t>v. 搜寻;翻找;乱翻 n. 翻箱倒柜的寻找</t>
-  </si>
-  <si>
-    <t>I rummage in my pocket for my glasses. 我在口袋里摸索找眼镜。</t>
-  </si>
-  <si>
-    <t>scorch [skɔːrtʃ]</t>
-  </si>
-  <si>
-    <t>v. 烤得变色;(使)烧焦</t>
-  </si>
-  <si>
-    <t>The leaves will scorch in hot sunshine. 这些叶子在酷热的阳光下会枯黄。</t>
-  </si>
-  <si>
-    <t>eject [ɪˈdʒekt]</t>
-  </si>
-  <si>
-    <t>v. 喷射;喷出;驱逐;逐出</t>
-  </si>
-  <si>
-    <t>Officials used guard dogs to eject the protesters. 官员们用警犬驱散抗议人群。</t>
-  </si>
-  <si>
-    <t>escalator [ˈeskəleɪtər]</t>
-  </si>
-  <si>
-    <t>n. 自动扶梯;电动扶梯</t>
-  </si>
-  <si>
-    <t>The down escalator is not running today. 今天下行的自动楼梯不运作。</t>
-  </si>
-  <si>
-    <t>eloquent [ˈeləkwənt]</t>
-  </si>
-  <si>
-    <t>adj. 雄辩的;有口才的;有说服力的</t>
-  </si>
-  <si>
-    <t>Her enthusiasm made her eloquent. 她的热情使她讲起话来口才流利。</t>
-  </si>
-  <si>
-    <t>tong [tɒŋ]</t>
-  </si>
-  <si>
-    <t>v. 用钳子钳起 n. 堂;钳;帮会</t>
-  </si>
-  <si>
-    <t>They don't like using this big tong. 他们不喜爱用这个大钳。</t>
-  </si>
-  <si>
-    <t>shareholder [ˈʃerhəʊldər]</t>
-  </si>
-  <si>
-    <t>n. 股东;持股人</t>
-  </si>
-  <si>
-    <t>the annual shareholders' meeting 一年一度的股东大会</t>
-  </si>
-  <si>
-    <t>glassware [ˈɡlæswer]</t>
-  </si>
-  <si>
-    <t>n. 玻璃制品</t>
-  </si>
-  <si>
-    <t>chemical glassware 化学玻璃器皿</t>
-  </si>
-  <si>
-    <t>merge [mɜːrdʒ]</t>
-  </si>
-  <si>
-    <t>v. 合并;混入;融合;渐渐消失</t>
-  </si>
-  <si>
-    <t>The rivers merge. 这些河流交汇在一起。</t>
-  </si>
-  <si>
-    <t>meticulous [məˈtɪkjələs]</t>
-  </si>
-  <si>
-    <t>adj. 一丝不苟的;缜密的</t>
-  </si>
-  <si>
-    <t>He is noted for his meticulous scholarship. 他以治学严谨著称。</t>
-  </si>
-  <si>
-    <t>immoderate [ɪˈmɑːdərət]</t>
-  </si>
-  <si>
-    <t>adj. 无节制的;不适中的;过度的</t>
-  </si>
-  <si>
-    <t>immoderate spending 过度花费</t>
-  </si>
-  <si>
-    <t>malice [ˈmælɪs]</t>
-  </si>
-  <si>
-    <t>n. 恶意;怨恨;蓄意</t>
-  </si>
-  <si>
-    <t>She did it out of malice. 她出于恶意做了这件事。</t>
-  </si>
-  <si>
-    <t>imperil [ɪmˈperəl]</t>
-  </si>
-  <si>
-    <t>v. 使陷于危险;危及</t>
-  </si>
-  <si>
-    <t>Your carelessness will imperil the whole company. 你的粗心大意会危及到整个公司。</t>
-  </si>
-  <si>
-    <t>manifestation [ˌmænɪfeˈsteɪʃ(ə)n]</t>
-  </si>
-  <si>
-    <t>n. 表示;显示;示威</t>
-  </si>
-  <si>
-    <t>That manifestation showed our power. 那次示威运动显示了我们的力量。</t>
-  </si>
-  <si>
-    <t>ornery [ˈɔːrnəri]</t>
-  </si>
-  <si>
-    <t>adj. 脾气坏的;难相处的</t>
-  </si>
-  <si>
-    <t>an ornery and venomous-tongued old lady 一个毒舌、难相处的老女人</t>
-  </si>
-  <si>
-    <t>household appliance [ˈhaʊshəʊld əˈplaɪəns]</t>
-  </si>
-  <si>
-    <t>phrase. 家用电器</t>
-  </si>
-  <si>
-    <t>Microwave oven is a common household appliance. 微波炉是一种常见的家用电器。</t>
-  </si>
-  <si>
-    <t>evasion [ɪˈveɪʒ(ə)n]</t>
-  </si>
-  <si>
-    <t>n. 逃避;回避 invasion:侵犯，侵略 envisage envision</t>
-  </si>
-  <si>
-    <t>She was fined for tax evasion. 她因逃税而被罚款。</t>
-  </si>
-  <si>
-    <t>revision [rɪˈvɪʒ(ə)n]</t>
-  </si>
-  <si>
-    <t>n. 修订;修改;复习</t>
-  </si>
-  <si>
-    <t>The dictionary is under revision. 这部词典正在修订之中。</t>
-  </si>
-  <si>
-    <t>impetuous [ɪmˈpetʃuəs]</t>
-  </si>
-  <si>
-    <t>adj. 鲁莽的;冲动的</t>
-  </si>
-  <si>
-    <t>She regretted her impetuous decision. 她后悔自己的鲁莽决定。</t>
-  </si>
-  <si>
-    <t>humanist [ˈhjuːmənɪst]</t>
-  </si>
-  <si>
-    <t>n. 人文主义者;人道主义者</t>
-  </si>
-  <si>
-    <t>a well-known humanist 一位著名的人道主义者</t>
-  </si>
-  <si>
-    <t>ignite [ɪɡˈnaɪt]</t>
-  </si>
-  <si>
-    <t>v. 点燃;使燃烧;激起</t>
-  </si>
-  <si>
-    <t>You ignite a match by scratching it. 划火柴就可让火柴燃起来。</t>
-  </si>
-  <si>
-    <t>kerosene [ˈkerəsiːn]</t>
-  </si>
-  <si>
-    <t>n. 煤油</t>
-  </si>
-  <si>
-    <t>demand for kerosene 对煤油的需求</t>
-  </si>
-  <si>
-    <t>lewd [luːd]</t>
-  </si>
-  <si>
-    <t>adj. 淫荡的;猥亵的;好色的</t>
-  </si>
-  <si>
-    <t>lewd thoughts 淫思色欲</t>
-  </si>
-  <si>
-    <t>intricate [ˈɪntrɪkət]</t>
-  </si>
-  <si>
-    <t>adj. 错综复杂的</t>
-  </si>
-  <si>
-    <t>I have a novel with an intricate plot. 我有一本情节错综复杂的小说。</t>
-  </si>
-  <si>
-    <t>piety [ˈpaɪəti]</t>
-  </si>
-  <si>
-    <t>n. 虔诚;虔敬</t>
-  </si>
-  <si>
-    <t>The priest was known for his piety. 这位牧师以虔诚而著称。</t>
-  </si>
-  <si>
-    <t>reciprocal [rɪˈsɪprək(ə)l]</t>
-  </si>
-  <si>
-    <t>adj. 互惠的;相互的</t>
-  </si>
-  <si>
-    <t>They show reciprocal affection to each other. 他们表达了彼此之间的爱慕。</t>
-  </si>
-  <si>
-    <t>range [reɪndʒ]</t>
-  </si>
-  <si>
-    <t>n. (变化)范围;一系列;山脉 v. 包括(各种不同的人或物);(在某范围内)变化</t>
-  </si>
-  <si>
-    <t>The salesman ranged the goods in order. 售货员把商品排列得很整齐。</t>
-  </si>
-  <si>
-    <t>prosper [ˈprɑːspər]</t>
-  </si>
-  <si>
-    <t>v. 成功;繁荣</t>
-  </si>
-  <si>
-    <t>Nothing will prosper in his hands. 在他手里什么事也办不成。</t>
-  </si>
-  <si>
-    <t>quality [ˈkwɑːləti]</t>
-  </si>
-  <si>
-    <t>n. 质量;素质;品质</t>
-  </si>
-  <si>
-    <t>He shows quality of leadership. 他显示出领导才能。</t>
-  </si>
-  <si>
-    <t>sneak [sniːk]</t>
-  </si>
-  <si>
-    <t>v. 溜;偷偷地做 adj. 突然的;出其不意的 n. 鬼鬼祟祟的人;偷偷摸摸</t>
-  </si>
-  <si>
-    <t>I sneak a look at his book. 我偷偷地看一眼他的书。</t>
-  </si>
-  <si>
-    <t>quake [kweɪk]</t>
-  </si>
-  <si>
-    <t>v. 震动;颤抖 n. 震动;地震</t>
-  </si>
-  <si>
-    <t>The sound of quake is very terrible. 震动的声音很吓人。</t>
-  </si>
-  <si>
-    <t>a fat salary [ə fæt ˈsæləri]</t>
-  </si>
-  <si>
-    <t>phrase. 高薪;优厚薪水</t>
-  </si>
-  <si>
-    <t>Our company will offer you a fat salary. 我们公司会给你提供优厚薪水。</t>
-  </si>
-  <si>
-    <t>detail [ˈdiːteɪl]</t>
-  </si>
-  <si>
-    <t>n. 细节;详情 v. 详细说明</t>
-  </si>
-  <si>
-    <t>He told us the accident in detail. 他详细地把事故讲给我们听。</t>
-  </si>
-  <si>
-    <t>bound [baʊnd]</t>
-  </si>
-  <si>
-    <t>adj. 有义务的;受约束的;必定的 v. 跳跃;限制;“bind”的过去式和过去分词 n. 跳跃;界限;限制</t>
-  </si>
-  <si>
-    <t>You are not legally bound to answer these questions. 在法律上你没有义务必须回答这些问题。</t>
-  </si>
-  <si>
-    <t>ancient [ˈeɪnʃənt]</t>
-  </si>
-  <si>
-    <t>adj. 古代的;古老的 n. 古人</t>
-  </si>
-  <si>
-    <t>He found a piece of fossil of an ancient bird. 他发现了一块古代鸟类的化石。</t>
+    <t>confidence [kɒnfɪdəns]</t>
+  </si>
+  <si>
+    <t>n.信心;信任;秘密;私事</t>
+  </si>
+  <si>
+    <t>He has won her confidence and she trusts him. 他已得到她的信任,她相信他。</t>
+  </si>
+  <si>
+    <t>newspaper [ˈnjuːzpeɪpə(r)]</t>
+  </si>
+  <si>
+    <t>报纸</t>
+  </si>
+  <si>
+    <t>I learned this news from the newspaper. 我从报纸上得知这个消息。</t>
+  </si>
+  <si>
+    <t>fifth [fɪfθ]</t>
+  </si>
+  <si>
+    <t>n.第五;五分之一 adj 第五的 adv 第五</t>
+  </si>
+  <si>
+    <t>You are the fifth. 你是第五名。</t>
+  </si>
+  <si>
+    <t>foreign [ˈfɒrən]</t>
+  </si>
+  <si>
+    <t>adj.外国的;外来的</t>
+  </si>
+  <si>
+    <t>foreign trade 对外贸易</t>
+  </si>
+  <si>
+    <t>autonomy [ɔːˈtɒnəmi]</t>
+  </si>
+  <si>
+    <t>n.自治;自主权;自治权</t>
+  </si>
+  <si>
+    <t>There are minority autonomy areas in China. 中国有少数民族自治区。</t>
+  </si>
+  <si>
+    <t>vision [ˈvɪʒ(ə)n]</t>
+  </si>
+  <si>
+    <t>n.视野;视力;想象;幻象</t>
+  </si>
+  <si>
+    <t>This travel broadened my vision and knowledge: 这次旅游拓宽了我的视野和知识。</t>
+  </si>
+  <si>
+    <t>authenticate [ɔːˈθentɪkeɪt]</t>
+  </si>
+  <si>
+    <t>v.证明是真实的;鉴别</t>
+  </si>
+  <si>
+    <t>authenticate user 证明用户的真实身份</t>
+  </si>
+  <si>
+    <t>Manila [məˈnɪlə]</t>
+  </si>
+  <si>
+    <t>n.马尼拉(菲律宾首都);马尼拉纸</t>
+  </si>
+  <si>
+    <t>the manila envelope 马尼拉纸制成的信封</t>
+  </si>
+  <si>
+    <t>attempt [əˈtempt]</t>
+  </si>
+  <si>
+    <t>n.企图;试图 v.企图;试图</t>
+  </si>
+  <si>
+    <t>Never attempt to overtake. 不要企图超车。</t>
+  </si>
+  <si>
+    <t>capitalize [ˈkæpɪtəlaɪz]</t>
+  </si>
+  <si>
+    <t>v.用大写字母书写;作为资本;提供资金;利用</t>
+  </si>
+  <si>
+    <t>Capitalize the letter. 大写这个字母。</t>
+  </si>
+  <si>
+    <t>cannibalism [ˈkænɪbəlɪzəm]</t>
+  </si>
+  <si>
+    <t>n.同类相食;食人肉</t>
+  </si>
+  <si>
+    <t>They were forced to practise cannibalism in order to survive. 为了生存,他们被迫同类相食。</t>
+  </si>
+  <si>
+    <t>wood [wʊd]</t>
+  </si>
+  <si>
+    <t>n.木材;木头</t>
+  </si>
+  <si>
+    <t>a pile of wood 一堆木头</t>
+  </si>
+  <si>
+    <t>residential college [ˌrezɪˈdenʃ(ə)l ˈkɒlɪdʒ]</t>
+  </si>
+  <si>
+    <t>phrase 寄宿制学院</t>
+  </si>
+  <si>
+    <t>the fee of residential college 住宿学院费</t>
+  </si>
+  <si>
+    <t>International Direct Dialing [ˌɪntəˈnæʃnəl daɪˈrekt ˈdaɪəlɪŋ]</t>
+  </si>
+  <si>
+    <t>n.国际直接拨号;国际直拨</t>
+  </si>
+  <si>
+    <t>Competition has resulted in a substantial reduction in International Direct Dialing call rates and improved service quality. 市场竞争使国际直通电话服务的收费大幅下降,但服务质素却更胜从前。</t>
+  </si>
+  <si>
+    <t>greyhound [ˈɡreɪhaʊnd]</t>
+  </si>
+  <si>
+    <t>n.灰狗</t>
+  </si>
+  <si>
+    <t>A greyhound has long thin legs. 灰狗的腿细又长。</t>
+  </si>
+  <si>
+    <t>make-believe [ˈmeɪk bɪliːv]</t>
+  </si>
+  <si>
+    <t>n.虚构;虚幻;假装 adj 假装的;虚构的</t>
+  </si>
+  <si>
+    <t>He asked in make-believe astonishment 他故作惊讶地问。</t>
+  </si>
+  <si>
+    <t>washing machine [ˈwɒʃɪŋ məˈʃiːn]</t>
+  </si>
+  <si>
+    <t>phrase 洗衣机</t>
+  </si>
+  <si>
+    <t>Our washing machine has broken. 我们的洗衣机坏了。</t>
+  </si>
+  <si>
+    <t>mitten [ˈmɪtn]</t>
+  </si>
+  <si>
+    <t>n.连指手套</t>
+  </si>
+  <si>
+    <t>leather mitten 皮革连指手套</t>
+  </si>
+  <si>
+    <t>millet [ˈmɪlɪt]</t>
+  </si>
+  <si>
+    <t>n.小米;粟</t>
+  </si>
+  <si>
+    <t>I have the millet for breakfast 我早餐吃小米。</t>
+  </si>
+  <si>
+    <t>community health [kəˈmjuːnəti helθ]</t>
+  </si>
+  <si>
+    <t>phrase 社区卫生</t>
+  </si>
+  <si>
+    <t>Improving family and community health is our duty and responsibility. 改善家庭和社区卫生是我们的责任与义务。</t>
+  </si>
+  <si>
+    <t>catching and throwing skill [ˈkætʃɪŋ ænd ˈθrəʊɪŋ skɪl]</t>
+  </si>
+  <si>
+    <t>phrase 抓举和投掷技巧</t>
+  </si>
+  <si>
+    <t>She thinks that the discus catching and throwing skill training should begin with basic training 铁饼的抓举和投掷技巧训练要从基础训练开始。</t>
+  </si>
+  <si>
+    <t>degree in psychology [dɪˈɡriː ɪn saɪˈkɒlədʒi]</t>
+  </si>
+  <si>
+    <t>phrase 心理学学位</t>
+  </si>
+  <si>
+    <t>Many people with a bachelor's degree in psychology find work in other unrelated fields. 许多有心理学学士学位的人找的工作是不在在其相关领域的。</t>
+  </si>
+  <si>
+    <t>leg-room [ˈleɡruːm]</t>
+  </si>
+  <si>
+    <t>n.座位前放腿处</t>
+  </si>
+  <si>
+    <t>The leg-room on the train is not enough for me. 火车座位前放腿的空间对我来说太小了。</t>
+  </si>
+  <si>
+    <t>domestic departure [dəˈmestɪk dɪˈpɑːrtʃər]</t>
+  </si>
+  <si>
+    <t>phrase 国内航班出站</t>
+  </si>
+  <si>
+    <t>You should go to the domestic departure hall to wait. 你该去国内航班出站厅候机。</t>
+  </si>
+  <si>
+    <t>departure gate [dɪˈpɑːrtʃər ɡeɪt]</t>
+  </si>
+  <si>
+    <t>phrase 登机口</t>
+  </si>
+  <si>
+    <t>Which is my departure gate? 我的登机口是哪个?</t>
+  </si>
+  <si>
+    <t>international departure [ˌɪntəˈnæʃnəl dɪˈpɑːrtʃər]</t>
+  </si>
+  <si>
+    <t>phrase 国际航班出港</t>
+  </si>
+  <si>
+    <t>Souvenir shops are available at the international departure hall. 国际航班出港大厅有纪念商品店。</t>
+  </si>
+  <si>
+    <t>stated [ˈsteɪtɪd]</t>
+  </si>
+  <si>
+    <t>adj.规定的;定期的;固定的 v.说明;陈述;声明;规定;“state”的过去式和过去分词</t>
+  </si>
+  <si>
+    <t>Generally magazines come out at stated periods. 一般来说,杂志定时出版。</t>
+  </si>
+  <si>
+    <t>blind alley [ˌblaɪnd ˈæli]</t>
+  </si>
+  <si>
+    <t>phrase 死胡同;绝路</t>
+  </si>
+  <si>
+    <t>The blind alley ended in a stone wall. 死胡同的尽头是一堵石墙。</t>
+  </si>
+  <si>
+    <t>mailman [ˈmeɪlmæn]</t>
+  </si>
+  <si>
+    <t>n.邮递员</t>
+  </si>
+  <si>
+    <t>The mailman delivers the mail twice a day in this area. 这个地区的邮差每天送两次信。</t>
+  </si>
+  <si>
+    <t>enrollment fee [ɪnˈrəʊlmənt fiː]</t>
+  </si>
+  <si>
+    <t>phrase 注册费;报名费</t>
+  </si>
+  <si>
+    <t>How much is the enrollment fee? 注册费用是多少?</t>
+  </si>
+  <si>
+    <t>go against [ɡəʊ əˈɡeɪnst]</t>
+  </si>
+  <si>
+    <t>phrase 反对;违反;不利于</t>
+  </si>
+  <si>
+    <t>Don't do any thing that should go against his will. 不要做违背他心意的事。</t>
+  </si>
+  <si>
+    <t>Head Coach [hed kəʊtʃ]</t>
+  </si>
+  <si>
+    <t>主教练</t>
+  </si>
+  <si>
+    <t>Head Coach agreed to let me play as the striker in this game. 主教练同意让我这场比赛打前锋。</t>
+  </si>
+  <si>
+    <t>leading actor and actress [ˈliːdɪŋ ˈæktər ænd ˈæktrəs]</t>
+  </si>
+  <si>
+    <t>phrase 男女主角;主演</t>
+  </si>
+  <si>
+    <t>The leading actor and actress of this film are all stars. 这部电影的男女主演都是明星。</t>
+  </si>
+  <si>
+    <t>training sessions [ˈtreɪnɪŋ ˈseʃnz]</t>
+  </si>
+  <si>
+    <t>phrase 培训课程</t>
+  </si>
+  <si>
+    <t>Training sessions will be held for new employees. 新员工会参加培训。</t>
+  </si>
+  <si>
+    <t>promiscuity [ˌprɒmɪˈskjuːəti]</t>
+  </si>
+  <si>
+    <t>n.淫乱;混交;杂乱</t>
+  </si>
+  <si>
+    <t>There also no doubt that she falls into promiscuity at last. 同时无疑她最后也堕入淫乱之中。</t>
+  </si>
+  <si>
+    <t>underground water [ˈʌndəɡraʊnd ˈwɔːtə(r)]</t>
+  </si>
+  <si>
+    <t>phrase 地下水</t>
+  </si>
+  <si>
+    <t>In general, the quality of underground water is good. 地下水水质总体良好。</t>
+  </si>
+  <si>
+    <t>preserve [prɪˈzɜːv]</t>
+  </si>
+  <si>
+    <t>v.保存;保护;保持 n.(某群体)专有的活动;保护区</t>
+  </si>
+  <si>
+    <t>We must preserve our natural resources. 我们必须保护自然资源。</t>
+  </si>
+  <si>
+    <t>consult [kənˈsʌlt]</t>
+  </si>
+  <si>
+    <t>v.咨询;查询;请教</t>
+  </si>
+  <si>
+    <t>consult a lawyer 咨询律师</t>
+  </si>
+  <si>
+    <t>ambition [æmˈbɪʃ(ə)n]</t>
+  </si>
+  <si>
+    <t>n.野心;雄心;抱复</t>
+  </si>
+  <si>
+    <t>There are no bounds to his ambition. 他的野心是无止境的。</t>
+  </si>
+  <si>
+    <t>acclimatize [əˈklaɪmətaɪz]</t>
+  </si>
+  <si>
+    <t>v.使适应(新气候或环境)</t>
+  </si>
+  <si>
+    <t>It took him two days to acclimatize to the life here. 他用了两天才适应这里的生活。</t>
   </si>
 </sst>
 </file>
@@ -447,18 +420,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -799,7 +771,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -808,17 +780,32 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
+      <left style="medium">
+        <color rgb="FF1F1F1F"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color rgb="FF1F1F1F"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
+      <top style="medium">
+        <color rgb="FF1F1F1F"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="medium">
+        <color rgb="FF1F1F1F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -944,7 +931,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -956,34 +943,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1068,11 +1055,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1420,16 +1416,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="56.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="36.375" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="46.625" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1443,607 +1440,589 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:4">
-      <c r="A2" s="1">
-        <v>128</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" s="1" customFormat="1" ht="29.25" spans="1:4">
+      <c r="A2" s="3">
+        <v>215</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:4">
-      <c r="A3" s="1">
-        <v>129</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A3" s="3">
+        <v>216</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:4">
-      <c r="A4" s="1">
-        <v>130</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A4" s="3">
+        <v>217</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:4">
-      <c r="A5" s="1">
-        <v>131</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="5" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A5" s="4">
+        <v>218</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:4">
-      <c r="A6" s="1">
-        <v>132</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="6" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A6" s="3">
+        <v>219</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:4">
-      <c r="A7" s="1">
-        <v>133</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="7" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A7" s="3">
+        <v>220</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:4">
-      <c r="A8" s="1">
-        <v>134</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="8" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A8" s="4">
+        <v>221</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:4">
-      <c r="A9" s="1">
-        <v>135</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="9" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A9" s="3">
+        <v>222</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:4">
-      <c r="A10" s="1">
-        <v>136</v>
-      </c>
-      <c r="B10" s="1" t="s">
+    <row r="10" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A10" s="3">
+        <v>223</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:4">
-      <c r="A11" s="1">
-        <v>137</v>
-      </c>
-      <c r="B11" s="1" t="s">
+    <row r="11" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A11" s="3">
+        <v>224</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:4">
-      <c r="A12" s="1">
-        <v>138</v>
-      </c>
-      <c r="B12" s="1" t="s">
+    <row r="12" s="1" customFormat="1" ht="29.25" spans="1:4">
+      <c r="A12" s="3">
+        <v>225</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:4">
-      <c r="A13" s="1">
-        <v>139</v>
-      </c>
-      <c r="B13" s="1" t="s">
+    <row r="13" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A13" s="4">
+        <v>226</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:4">
-      <c r="A14" s="1">
-        <v>140</v>
-      </c>
-      <c r="B14" s="1" t="s">
+    <row r="14" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A14" s="4">
+        <v>227</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:4">
-      <c r="A15" s="1">
-        <v>141</v>
-      </c>
-      <c r="B15" s="1" t="s">
+    <row r="15" s="1" customFormat="1" ht="57.75" spans="1:4">
+      <c r="A15" s="3">
+        <v>228</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:4">
-      <c r="A16" s="1">
-        <v>142</v>
-      </c>
-      <c r="B16" s="1" t="s">
+    <row r="16" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A16" s="3">
+        <v>229</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="1:4">
-      <c r="A17" s="1">
-        <v>143</v>
-      </c>
-      <c r="B17" s="1" t="s">
+    <row r="17" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A17" s="3">
+        <v>230</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="1:4">
-      <c r="A18" s="1">
-        <v>144</v>
-      </c>
-      <c r="B18" s="1" t="s">
+    <row r="18" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A18" s="3">
+        <v>231</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="1:4">
-      <c r="A19" s="1">
-        <v>145</v>
-      </c>
-      <c r="B19" s="1" t="s">
+    <row r="19" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A19" s="4">
+        <v>232</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="1:4">
-      <c r="A20" s="1">
-        <v>146</v>
-      </c>
-      <c r="B20" s="1" t="s">
+    <row r="20" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A20" s="3">
+        <v>233</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="1:4">
-      <c r="A21" s="1">
-        <v>147</v>
-      </c>
-      <c r="B21" s="1" t="s">
+    <row r="21" s="1" customFormat="1" ht="42.75" spans="1:4">
+      <c r="A21" s="3">
+        <v>234</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="1:4">
-      <c r="A22" s="1">
-        <v>148</v>
-      </c>
-      <c r="B22" s="1" t="s">
+    <row r="22" s="1" customFormat="1" ht="42.75" spans="1:4">
+      <c r="A22" s="3">
+        <v>235</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="1:4">
-      <c r="A23" s="1">
-        <v>149</v>
-      </c>
-      <c r="B23" s="1" t="s">
+    <row r="23" s="1" customFormat="1" ht="42.75" spans="1:4">
+      <c r="A23" s="3">
+        <v>236</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="1:4">
-      <c r="A24" s="1">
-        <v>150</v>
-      </c>
-      <c r="B24" s="1" t="s">
+    <row r="24" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A24" s="3">
+        <v>237</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="1:4">
-      <c r="A25" s="1">
-        <v>151</v>
-      </c>
-      <c r="B25" s="1" t="s">
+    <row r="25" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A25" s="3">
+        <v>238</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="1:4">
-      <c r="A26" s="1">
-        <v>152</v>
-      </c>
-      <c r="B26" s="1" t="s">
+    <row r="26" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A26" s="3">
+        <v>239</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="1:4">
-      <c r="A27" s="1">
-        <v>153</v>
-      </c>
-      <c r="B27" s="1" t="s">
+    <row r="27" s="1" customFormat="1" ht="29.25" spans="1:4">
+      <c r="A27" s="3">
+        <v>240</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="1:4">
-      <c r="A28" s="1">
-        <v>154</v>
-      </c>
-      <c r="B28" s="1" t="s">
+    <row r="28" s="1" customFormat="1" ht="29.25" spans="1:4">
+      <c r="A28" s="3">
+        <v>241</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="1:4">
-      <c r="A29" s="1">
-        <v>155</v>
-      </c>
-      <c r="B29" s="1" t="s">
+    <row r="29" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A29" s="3">
+        <v>242</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="1:4">
-      <c r="A30" s="1">
-        <v>156</v>
-      </c>
-      <c r="B30" s="1" t="s">
+    <row r="30" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A30" s="3">
+        <v>243</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="1:4">
-      <c r="A31" s="1">
-        <v>157</v>
-      </c>
-      <c r="B31" s="1" t="s">
+    <row r="31" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A31" s="3">
+        <v>244</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="1:4">
-      <c r="A32" s="1">
-        <v>158</v>
-      </c>
-      <c r="B32" s="1" t="s">
+    <row r="32" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A32" s="3">
+        <v>245</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" spans="1:4">
-      <c r="A33" s="1">
-        <v>159</v>
-      </c>
-      <c r="B33" s="1" t="s">
+    <row r="33" s="1" customFormat="1" ht="29.25" spans="1:4">
+      <c r="A33" s="3">
+        <v>246</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="1:4">
-      <c r="A34" s="1">
-        <v>160</v>
-      </c>
-      <c r="B34" s="1" t="s">
+    <row r="34" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A34" s="3">
+        <v>247</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="1:4">
-      <c r="A35" s="1">
-        <v>161</v>
-      </c>
-      <c r="B35" s="1" t="s">
+    <row r="35" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A35" s="3">
+        <v>248</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" spans="1:4">
-      <c r="A36" s="1">
-        <v>162</v>
-      </c>
-      <c r="B36" s="1" t="s">
+    <row r="36" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A36" s="3">
+        <v>249</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" spans="1:4">
-      <c r="A37" s="1">
-        <v>163</v>
-      </c>
-      <c r="B37" s="1" t="s">
+    <row r="37" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A37" s="3">
+        <v>250</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="1:4">
-      <c r="A38" s="1">
-        <v>164</v>
-      </c>
-      <c r="B38" s="1" t="s">
+    <row r="38" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A38" s="3">
+        <v>251</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" spans="1:4">
-      <c r="A39" s="1">
-        <v>165</v>
-      </c>
-      <c r="B39" s="1" t="s">
+    <row r="39" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A39" s="4">
+        <v>252</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" spans="1:4">
-      <c r="A40" s="1">
-        <v>166</v>
-      </c>
-      <c r="B40" s="1" t="s">
+    <row r="40" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A40" s="3">
+        <v>253</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" spans="1:4">
-      <c r="A41" s="1">
-        <v>167</v>
-      </c>
-      <c r="B41" s="1" t="s">
+    <row r="41" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A41" s="3">
+        <v>254</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" spans="1:4">
-      <c r="A42" s="1">
-        <v>168</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:4">
-      <c r="A43" s="1">
-        <v>169</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="1:4">
-      <c r="A44" s="1">
-        <v>170</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>132</v>
-      </c>
+    <row r="42" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="14.25" spans="1:4">
+      <c r="A44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+    </row>
+    <row r="45" ht="14.25" spans="1:4">
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/input.xlsx
+++ b/input.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>序号</t>
   </si>
@@ -41,364 +41,391 @@
     <t>例句</t>
   </si>
   <si>
-    <t>confidence [kɒnfɪdəns]</t>
-  </si>
-  <si>
-    <t>n.信心;信任;秘密;私事</t>
-  </si>
-  <si>
-    <t>He has won her confidence and she trusts him. 他已得到她的信任,她相信他。</t>
-  </si>
-  <si>
-    <t>newspaper [ˈnjuːzpeɪpə(r)]</t>
-  </si>
-  <si>
-    <t>报纸</t>
-  </si>
-  <si>
-    <t>I learned this news from the newspaper. 我从报纸上得知这个消息。</t>
-  </si>
-  <si>
-    <t>fifth [fɪfθ]</t>
-  </si>
-  <si>
-    <t>n.第五;五分之一 adj 第五的 adv 第五</t>
-  </si>
-  <si>
-    <t>You are the fifth. 你是第五名。</t>
-  </si>
-  <si>
-    <t>foreign [ˈfɒrən]</t>
-  </si>
-  <si>
-    <t>adj.外国的;外来的</t>
-  </si>
-  <si>
-    <t>foreign trade 对外贸易</t>
-  </si>
-  <si>
-    <t>autonomy [ɔːˈtɒnəmi]</t>
-  </si>
-  <si>
-    <t>n.自治;自主权;自治权</t>
-  </si>
-  <si>
-    <t>There are minority autonomy areas in China. 中国有少数民族自治区。</t>
-  </si>
-  <si>
-    <t>vision [ˈvɪʒ(ə)n]</t>
-  </si>
-  <si>
-    <t>n.视野;视力;想象;幻象</t>
-  </si>
-  <si>
-    <t>This travel broadened my vision and knowledge: 这次旅游拓宽了我的视野和知识。</t>
-  </si>
-  <si>
-    <t>authenticate [ɔːˈθentɪkeɪt]</t>
-  </si>
-  <si>
-    <t>v.证明是真实的;鉴别</t>
-  </si>
-  <si>
-    <t>authenticate user 证明用户的真实身份</t>
-  </si>
-  <si>
-    <t>Manila [məˈnɪlə]</t>
-  </si>
-  <si>
-    <t>n.马尼拉(菲律宾首都);马尼拉纸</t>
-  </si>
-  <si>
-    <t>the manila envelope 马尼拉纸制成的信封</t>
-  </si>
-  <si>
-    <t>attempt [əˈtempt]</t>
-  </si>
-  <si>
-    <t>n.企图;试图 v.企图;试图</t>
-  </si>
-  <si>
-    <t>Never attempt to overtake. 不要企图超车。</t>
-  </si>
-  <si>
-    <t>capitalize [ˈkæpɪtəlaɪz]</t>
-  </si>
-  <si>
-    <t>v.用大写字母书写;作为资本;提供资金;利用</t>
-  </si>
-  <si>
-    <t>Capitalize the letter. 大写这个字母。</t>
-  </si>
-  <si>
-    <t>cannibalism [ˈkænɪbəlɪzəm]</t>
-  </si>
-  <si>
-    <t>n.同类相食;食人肉</t>
-  </si>
-  <si>
-    <t>They were forced to practise cannibalism in order to survive. 为了生存,他们被迫同类相食。</t>
-  </si>
-  <si>
-    <t>wood [wʊd]</t>
-  </si>
-  <si>
-    <t>n.木材;木头</t>
-  </si>
-  <si>
-    <t>a pile of wood 一堆木头</t>
-  </si>
-  <si>
-    <t>residential college [ˌrezɪˈdenʃ(ə)l ˈkɒlɪdʒ]</t>
-  </si>
-  <si>
-    <t>phrase 寄宿制学院</t>
-  </si>
-  <si>
-    <t>the fee of residential college 住宿学院费</t>
-  </si>
-  <si>
-    <t>International Direct Dialing [ˌɪntəˈnæʃnəl daɪˈrekt ˈdaɪəlɪŋ]</t>
-  </si>
-  <si>
-    <t>n.国际直接拨号;国际直拨</t>
-  </si>
-  <si>
-    <t>Competition has resulted in a substantial reduction in International Direct Dialing call rates and improved service quality. 市场竞争使国际直通电话服务的收费大幅下降,但服务质素却更胜从前。</t>
-  </si>
-  <si>
-    <t>greyhound [ˈɡreɪhaʊnd]</t>
-  </si>
-  <si>
-    <t>n.灰狗</t>
-  </si>
-  <si>
-    <t>A greyhound has long thin legs. 灰狗的腿细又长。</t>
-  </si>
-  <si>
-    <t>make-believe [ˈmeɪk bɪliːv]</t>
-  </si>
-  <si>
-    <t>n.虚构;虚幻;假装 adj 假装的;虚构的</t>
-  </si>
-  <si>
-    <t>He asked in make-believe astonishment 他故作惊讶地问。</t>
-  </si>
-  <si>
-    <t>washing machine [ˈwɒʃɪŋ məˈʃiːn]</t>
-  </si>
-  <si>
-    <t>phrase 洗衣机</t>
-  </si>
-  <si>
-    <t>Our washing machine has broken. 我们的洗衣机坏了。</t>
-  </si>
-  <si>
-    <t>mitten [ˈmɪtn]</t>
-  </si>
-  <si>
-    <t>n.连指手套</t>
-  </si>
-  <si>
-    <t>leather mitten 皮革连指手套</t>
-  </si>
-  <si>
-    <t>millet [ˈmɪlɪt]</t>
-  </si>
-  <si>
-    <t>n.小米;粟</t>
-  </si>
-  <si>
-    <t>I have the millet for breakfast 我早餐吃小米。</t>
-  </si>
-  <si>
-    <t>community health [kəˈmjuːnəti helθ]</t>
-  </si>
-  <si>
-    <t>phrase 社区卫生</t>
-  </si>
-  <si>
-    <t>Improving family and community health is our duty and responsibility. 改善家庭和社区卫生是我们的责任与义务。</t>
-  </si>
-  <si>
-    <t>catching and throwing skill [ˈkætʃɪŋ ænd ˈθrəʊɪŋ skɪl]</t>
-  </si>
-  <si>
-    <t>phrase 抓举和投掷技巧</t>
-  </si>
-  <si>
-    <t>She thinks that the discus catching and throwing skill training should begin with basic training 铁饼的抓举和投掷技巧训练要从基础训练开始。</t>
-  </si>
-  <si>
-    <t>degree in psychology [dɪˈɡriː ɪn saɪˈkɒlədʒi]</t>
-  </si>
-  <si>
-    <t>phrase 心理学学位</t>
-  </si>
-  <si>
-    <t>Many people with a bachelor's degree in psychology find work in other unrelated fields. 许多有心理学学士学位的人找的工作是不在在其相关领域的。</t>
-  </si>
-  <si>
-    <t>leg-room [ˈleɡruːm]</t>
-  </si>
-  <si>
-    <t>n.座位前放腿处</t>
-  </si>
-  <si>
-    <t>The leg-room on the train is not enough for me. 火车座位前放腿的空间对我来说太小了。</t>
-  </si>
-  <si>
-    <t>domestic departure [dəˈmestɪk dɪˈpɑːrtʃər]</t>
-  </si>
-  <si>
-    <t>phrase 国内航班出站</t>
-  </si>
-  <si>
-    <t>You should go to the domestic departure hall to wait. 你该去国内航班出站厅候机。</t>
-  </si>
-  <si>
-    <t>departure gate [dɪˈpɑːrtʃər ɡeɪt]</t>
-  </si>
-  <si>
-    <t>phrase 登机口</t>
-  </si>
-  <si>
-    <t>Which is my departure gate? 我的登机口是哪个?</t>
-  </si>
-  <si>
-    <t>international departure [ˌɪntəˈnæʃnəl dɪˈpɑːrtʃər]</t>
-  </si>
-  <si>
-    <t>phrase 国际航班出港</t>
-  </si>
-  <si>
-    <t>Souvenir shops are available at the international departure hall. 国际航班出港大厅有纪念商品店。</t>
-  </si>
-  <si>
-    <t>stated [ˈsteɪtɪd]</t>
-  </si>
-  <si>
-    <t>adj.规定的;定期的;固定的 v.说明;陈述;声明;规定;“state”的过去式和过去分词</t>
-  </si>
-  <si>
-    <t>Generally magazines come out at stated periods. 一般来说,杂志定时出版。</t>
-  </si>
-  <si>
-    <t>blind alley [ˌblaɪnd ˈæli]</t>
-  </si>
-  <si>
-    <t>phrase 死胡同;绝路</t>
-  </si>
-  <si>
-    <t>The blind alley ended in a stone wall. 死胡同的尽头是一堵石墙。</t>
-  </si>
-  <si>
-    <t>mailman [ˈmeɪlmæn]</t>
-  </si>
-  <si>
-    <t>n.邮递员</t>
-  </si>
-  <si>
-    <t>The mailman delivers the mail twice a day in this area. 这个地区的邮差每天送两次信。</t>
-  </si>
-  <si>
-    <t>enrollment fee [ɪnˈrəʊlmənt fiː]</t>
-  </si>
-  <si>
-    <t>phrase 注册费;报名费</t>
-  </si>
-  <si>
-    <t>How much is the enrollment fee? 注册费用是多少?</t>
-  </si>
-  <si>
-    <t>go against [ɡəʊ əˈɡeɪnst]</t>
-  </si>
-  <si>
-    <t>phrase 反对;违反;不利于</t>
-  </si>
-  <si>
-    <t>Don't do any thing that should go against his will. 不要做违背他心意的事。</t>
-  </si>
-  <si>
-    <t>Head Coach [hed kəʊtʃ]</t>
-  </si>
-  <si>
-    <t>主教练</t>
-  </si>
-  <si>
-    <t>Head Coach agreed to let me play as the striker in this game. 主教练同意让我这场比赛打前锋。</t>
-  </si>
-  <si>
-    <t>leading actor and actress [ˈliːdɪŋ ˈæktər ænd ˈæktrəs]</t>
-  </si>
-  <si>
-    <t>phrase 男女主角;主演</t>
-  </si>
-  <si>
-    <t>The leading actor and actress of this film are all stars. 这部电影的男女主演都是明星。</t>
-  </si>
-  <si>
-    <t>training sessions [ˈtreɪnɪŋ ˈseʃnz]</t>
-  </si>
-  <si>
-    <t>phrase 培训课程</t>
-  </si>
-  <si>
-    <t>Training sessions will be held for new employees. 新员工会参加培训。</t>
-  </si>
-  <si>
-    <t>promiscuity [ˌprɒmɪˈskjuːəti]</t>
-  </si>
-  <si>
-    <t>n.淫乱;混交;杂乱</t>
-  </si>
-  <si>
-    <t>There also no doubt that she falls into promiscuity at last. 同时无疑她最后也堕入淫乱之中。</t>
-  </si>
-  <si>
-    <t>underground water [ˈʌndəɡraʊnd ˈwɔːtə(r)]</t>
-  </si>
-  <si>
-    <t>phrase 地下水</t>
-  </si>
-  <si>
-    <t>In general, the quality of underground water is good. 地下水水质总体良好。</t>
-  </si>
-  <si>
-    <t>preserve [prɪˈzɜːv]</t>
-  </si>
-  <si>
-    <t>v.保存;保护;保持 n.(某群体)专有的活动;保护区</t>
-  </si>
-  <si>
-    <t>We must preserve our natural resources. 我们必须保护自然资源。</t>
-  </si>
-  <si>
-    <t>consult [kənˈsʌlt]</t>
-  </si>
-  <si>
-    <t>v.咨询;查询;请教</t>
-  </si>
-  <si>
-    <t>consult a lawyer 咨询律师</t>
-  </si>
-  <si>
-    <t>ambition [æmˈbɪʃ(ə)n]</t>
-  </si>
-  <si>
-    <t>n.野心;雄心;抱复</t>
-  </si>
-  <si>
-    <t>There are no bounds to his ambition. 他的野心是无止境的。</t>
-  </si>
-  <si>
-    <t>acclimatize [əˈklaɪmətaɪz]</t>
-  </si>
-  <si>
-    <t>v.使适应(新气候或环境)</t>
-  </si>
-  <si>
-    <t>It took him two days to acclimatize to the life here. 他用了两天才适应这里的生活。</t>
+    <t>breakdown [bretk daun]</t>
+  </si>
+  <si>
+    <t>n.崩溃;倒塌;损坏;故障;细目分类</t>
+  </si>
+  <si>
+    <t>a breakdown of the costs 一份开支细目</t>
+  </si>
+  <si>
+    <t>grill [gral]</t>
+  </si>
+  <si>
+    <t>n.烤架;铁格子 v.烧烤:拷问</t>
+  </si>
+  <si>
+    <t>Grill the sausages for ten minutes. 把香肠烤十分钟。</t>
+  </si>
+  <si>
+    <t>theft [Beft]</t>
+  </si>
+  <si>
+    <t>n.偷窃;盗窃罪</t>
+  </si>
+  <si>
+    <t>He was put in prison for theft. 他因为偷窃被关进监狱。</t>
+  </si>
+  <si>
+    <t>jewel [dzu al]</t>
+  </si>
+  <si>
+    <t>宝石:珠宝</t>
+  </si>
+  <si>
+    <t>The crown was inlaid with a jewel. 皇冠上镶嵌着一颗珠宝。</t>
+  </si>
+  <si>
+    <t>lodge [lad3]</t>
+  </si>
+  <si>
+    <t>小舍;传达室 v.存放;借宿;提出(抗议)</t>
+  </si>
+  <si>
+    <t>He put the luggage in the lodge. 他把行李放在了传达室。</t>
+  </si>
+  <si>
+    <t>cloth [klo:0]</t>
+  </si>
+  <si>
+    <t>n.布;布料</t>
+  </si>
+  <si>
+    <t>a piece of cloth 一块布</t>
+  </si>
+  <si>
+    <t>unlikely [An'laikli]</t>
+  </si>
+  <si>
+    <t>adj.不大可能的;不一定有把握的</t>
+  </si>
+  <si>
+    <t>It seems unlikely that he will come. 他似乎不大可能来。</t>
+  </si>
+  <si>
+    <t>artery [artari]</t>
+  </si>
+  <si>
+    <t>n.动脉;干线;要道</t>
+  </si>
+  <si>
+    <t>Blood poured from the artery. 血从动脉涌出。</t>
+  </si>
+  <si>
+    <t>academic [ækademik]</t>
+  </si>
+  <si>
+    <t>adj.学院的;学术的 n.大学教师;学者</t>
+  </si>
+  <si>
+    <t>He has no interest in academic issues. 他对学术问题毫无兴趣。</t>
+  </si>
+  <si>
+    <t>vegetable [ ved Ztab( ]</t>
+  </si>
+  <si>
+    <t>蔬菜</t>
+  </si>
+  <si>
+    <t>I love the vegetable. 我喜欢蔬菜。</t>
+  </si>
+  <si>
+    <t>clearance [kitrans]</t>
+  </si>
+  <si>
+    <t>n. 清除;间隙;批准;放行</t>
+  </si>
+  <si>
+    <t>There is a clearance of only five inches. 只有五寸的间隙。</t>
+  </si>
+  <si>
+    <t>research project [ri's3:t prad Zekt]</t>
+  </si>
+  <si>
+    <t>phrase 研究项目</t>
+  </si>
+  <si>
+    <t>The research project was only a partial success. 那个研究项目只取得部分成功。</t>
+  </si>
+  <si>
+    <t>inspiration [Inspǝ'tel( )n]</t>
+  </si>
+  <si>
+    <t>n.灵感;鼓舞;启发</t>
+  </si>
+  <si>
+    <t>I cannot write without inspiration. 没有灵感我写不出东西。</t>
+  </si>
+  <si>
+    <t>opponent [Japaunant]</t>
+  </si>
+  <si>
+    <t>n.对手;反对者;敌手</t>
+  </si>
+  <si>
+    <t>beat the opponent 击败对手</t>
+  </si>
+  <si>
+    <t>confer with [kən'f3r w10]</t>
+  </si>
+  <si>
+    <t>phrase 和...商谈</t>
+  </si>
+  <si>
+    <t>I must confer with my lawyer before I decide 我必须先同我的律师商量一下才能做出决定。</t>
+  </si>
+  <si>
+    <t>appreciation [apri:fi'erftoin]</t>
+  </si>
+  <si>
+    <t>n.欣赏;感激;理解</t>
+  </si>
+  <si>
+    <t>An appreciation of art will enrich your life. 艺术欣赏将会丰富你的生活。</t>
+  </si>
+  <si>
+    <t>teenager [ti neld Zar]</t>
+  </si>
+  <si>
+    <t>n.(十三到十九岁的)青少年</t>
+  </si>
+  <si>
+    <t>It is not easy to educate teenagers. 教育青少年不是件容易的事。</t>
+  </si>
+  <si>
+    <t>photographer [fa'ta grafər]</t>
+  </si>
+  <si>
+    <t>n.摄影家;摄影师</t>
+  </si>
+  <si>
+    <t>I enjoy my job as a photographer. 我喜爱摄影师这份工作。</t>
+  </si>
+  <si>
+    <t>rocket [rakn]</t>
+  </si>
+  <si>
+    <t>n.火箭 v.飞速上升;骤增</t>
+  </si>
+  <si>
+    <t>space rocket 航天火箭</t>
+  </si>
+  <si>
+    <t>cargo [kargou]</t>
+  </si>
+  <si>
+    <t>n.货物</t>
+  </si>
+  <si>
+    <t>cargo ship 货船</t>
+  </si>
+  <si>
+    <t>sensible [ 'sensab ( ) ]</t>
+  </si>
+  <si>
+    <t>adj.明智的;有判断力的;恰当的;合理的</t>
+  </si>
+  <si>
+    <t>It was sensible of you to bring the umbrella. 你带雨伞很明智。</t>
+  </si>
+  <si>
+    <t>discharge [dis1[ard3]</t>
+  </si>
+  <si>
+    <t>v.放出;排出;开除;偿还债务;履行;卸货;放电 n.排放;排放出的物体</t>
+  </si>
+  <si>
+    <t>They discharge him from prison. 他们把他从监狱里放了出来。</t>
+  </si>
+  <si>
+    <t>coverage [kavarid 3]</t>
+  </si>
+  <si>
+    <t>n.覆盖范围:新闻报道;保险</t>
+  </si>
+  <si>
+    <t>This radio station has great coverage. 这个无线电台的覆盖范围很广。</t>
+  </si>
+  <si>
+    <t>contain no glass [kən'contain no glass]</t>
+  </si>
+  <si>
+    <t>phrase 不含玻璃</t>
+  </si>
+  <si>
+    <t>These products contain no glass, filaments or mercury. 这些产品不含玻璃、灯丝或汞。</t>
+  </si>
+  <si>
+    <t>hairy [hen]</t>
+  </si>
+  <si>
+    <t>adj.多毛的;惊险的</t>
+  </si>
+  <si>
+    <t>a hairy escape 惊险的逃生</t>
+  </si>
+  <si>
+    <t>hunger [hAngar]</t>
+  </si>
+  <si>
+    <t>n.饥饿;渴求 v.使饥饿;渴望</t>
+  </si>
+  <si>
+    <t>Hunger is often the mother of crime. 饥饿常是犯罪的根源。</t>
+  </si>
+  <si>
+    <t>booklet [buklot]</t>
+  </si>
+  <si>
+    <t>n.小册子</t>
+  </si>
+  <si>
+    <t>free booklet 免费的小册子</t>
+  </si>
+  <si>
+    <t>fountain [faunt( )n]</t>
+  </si>
+  <si>
+    <t>n. 喷泉;源泉</t>
+  </si>
+  <si>
+    <t>The fountain projects a stream of water. 喷泉喷出一股水。</t>
+  </si>
+  <si>
+    <t>boa</t>
+  </si>
+  <si>
+    <t>n.蟒蛇;女用毛皮长围巾</t>
+  </si>
+  <si>
+    <t>A boa constrictor squeezes its victims to death. 蟒蛇缠死它的猎物。</t>
+  </si>
+  <si>
+    <t>slam [shæm]</t>
+  </si>
+  <si>
+    <t>v. 砰地关上;猛地一动;抨击</t>
+  </si>
+  <si>
+    <t>Close the door carefully, don't slam it. 小心地关上门,别使劲摔。</t>
+  </si>
+  <si>
+    <t>blog [bla:g]</t>
+  </si>
+  <si>
+    <t>n.博客;网络随笔;日志 v. 在博客上发布文章</t>
+  </si>
+  <si>
+    <t>The blog saves one's experiences. 日志能记录一个人的历程。</t>
+  </si>
+  <si>
+    <t>blemish ['blemt ]</t>
+  </si>
+  <si>
+    <t>n.瑕疵;污点;缺点 v.玷污;损害</t>
+  </si>
+  <si>
+    <t>The scar is a blemish on her face. 这伤疤是她脸上的一个疵点。</t>
+  </si>
+  <si>
+    <t>auto</t>
+  </si>
+  <si>
+    <t>n.汽车(auto-作为前缀的时候表示“自动的”、“自己的”)</t>
+  </si>
+  <si>
+    <t>The company started its auto business in 1967. 该公司于1967年开始汽车生产。</t>
+  </si>
+  <si>
+    <t>lung [۱۸]</t>
+  </si>
+  <si>
+    <t>n.肺</t>
+  </si>
+  <si>
+    <t>A bullet pierced his right lung 一颗子弹洞穿他的右肺。</t>
+  </si>
+  <si>
+    <t>solo</t>
+  </si>
+  <si>
+    <t>adj.单独的 n.独奏;独唱;独舞 adv.单独地</t>
+  </si>
+  <si>
+    <t>The concert began with a piano solo. 音乐会以一首钢琴独奏开始。</t>
+  </si>
+  <si>
+    <t>Jeep [d3ip]</t>
+  </si>
+  <si>
+    <t>n.吉普车</t>
+  </si>
+  <si>
+    <t>The green jeep is made in China. 这辆绿色的吉普车是中国制造的。</t>
+  </si>
+  <si>
+    <t>resume [ri'zum]</t>
+  </si>
+  <si>
+    <t>v.(中断后)继续;重新开始 n.简历</t>
+  </si>
+  <si>
+    <t>The work will resume tomorrow 工作明天会再继续下去。</t>
+  </si>
+  <si>
+    <t>fuse [z]</t>
+  </si>
+  <si>
+    <t>n.保险丝;导火线;引信 v.由于保险丝烧断而电路不通;熔接;结合</t>
+  </si>
+  <si>
+    <t>We fuse copper and tin to make bronze. 我们把铜和锡熔制成青铜。</t>
+  </si>
+  <si>
+    <t>pursue [par'su:]</t>
+  </si>
+  <si>
+    <t>v.追求;追赶;追逐</t>
+  </si>
+  <si>
+    <t>The hounds pursue the fox. 猎犬们追赶那只狐狸。</t>
+  </si>
+  <si>
+    <t>paralyze [pærəlarz]</t>
+  </si>
+  <si>
+    <t>v.使麻痹;使瘫痪;使无效;使停止活动</t>
+  </si>
+  <si>
+    <t>strict regulations that paralyze economic activity 阻碍经济活动的严格规章制度</t>
+  </si>
+  <si>
+    <t>remaining [I'meInIn]</t>
+  </si>
+  <si>
+    <t>adj.剩余的;剩下的 v.剩下;留下;依然不变</t>
+  </si>
+  <si>
+    <t>The remaining journey has 700 miles. 剩下的这段旅程有七百英里。</t>
+  </si>
+  <si>
+    <t>odour ['sudor]</t>
+  </si>
+  <si>
+    <t>n.气味</t>
+  </si>
+  <si>
+    <t>He smells the odour of flowers. 他闻到花的气味。</t>
+  </si>
+  <si>
+    <t>trim [trim]</t>
+  </si>
+  <si>
+    <t>v.修剪;装饰 n.修剪 adj.苗条的;整洁的</t>
+  </si>
+  <si>
+    <t>He went to the barber's for a trim. 他去理发店给头发做修剪。</t>
   </si>
 </sst>
 </file>
@@ -771,7 +798,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -791,21 +818,6 @@
       </top>
       <bottom style="medium">
         <color rgb="FF1F1F1F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -931,7 +943,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -943,34 +955,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1055,20 +1067,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1440,589 +1449,613 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="29.25" spans="1:4">
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A2" s="3">
-        <v>215</v>
-      </c>
-      <c r="B2" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A3" s="3">
-        <v>216</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A3" s="4">
+        <v>300</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A4" s="3">
-        <v>217</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="4">
+        <v>301</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="5" s="1" customFormat="1" ht="28.5" spans="1:4">
       <c r="A5" s="4">
-        <v>218</v>
-      </c>
-      <c r="B5" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A6" s="3">
-        <v>219</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="4">
+        <v>303</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="28.5" spans="1:4">
+    <row r="7" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A7" s="3">
-        <v>220</v>
-      </c>
-      <c r="B7" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A8" s="4">
-        <v>221</v>
-      </c>
-      <c r="B8" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A9" s="3">
-        <v>222</v>
+      <c r="A9" s="4">
+        <v>306</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A10" s="3">
-        <v>223</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="10" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A10" s="4">
+        <v>307</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A11" s="3">
-        <v>224</v>
-      </c>
-      <c r="B11" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="29.25" spans="1:4">
-      <c r="A12" s="3">
-        <v>225</v>
-      </c>
-      <c r="B12" s="3" t="s">
+    <row r="12" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A12" s="4">
+        <v>309</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="13" s="1" customFormat="1" ht="28.5" spans="1:4">
       <c r="A13" s="4">
-        <v>226</v>
-      </c>
-      <c r="B13" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="14" s="1" customFormat="1" ht="28.5" spans="1:4">
       <c r="A14" s="4">
-        <v>227</v>
-      </c>
-      <c r="B14" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="57.75" spans="1:4">
+    <row r="15" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A15" s="3">
-        <v>228</v>
-      </c>
-      <c r="B15" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A16" s="3">
-        <v>229</v>
-      </c>
-      <c r="B16" s="3" t="s">
+    <row r="16" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A16" s="4">
+        <v>313</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A17" s="3">
-        <v>230</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="A17" s="4">
+        <v>314</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A18" s="3">
-        <v>231</v>
-      </c>
-      <c r="B18" s="3" t="s">
+    <row r="18" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A18" s="4">
+        <v>315</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="19" s="1" customFormat="1" ht="28.5" spans="1:4">
       <c r="A19" s="4">
-        <v>232</v>
-      </c>
-      <c r="B19" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A20" s="3">
-        <v>233</v>
-      </c>
-      <c r="B20" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="42.75" spans="1:4">
+    <row r="21" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A21" s="3">
-        <v>234</v>
-      </c>
-      <c r="B21" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="42.75" spans="1:4">
-      <c r="A22" s="3">
-        <v>235</v>
-      </c>
-      <c r="B22" s="3" t="s">
+    <row r="22" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A22" s="4">
+        <v>319</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="42.75" spans="1:4">
-      <c r="A23" s="3">
-        <v>236</v>
-      </c>
-      <c r="B23" s="3" t="s">
+    <row r="23" s="1" customFormat="1" ht="29.25" spans="1:4">
+      <c r="A23" s="4">
+        <v>320</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A24" s="3">
-        <v>237</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="A24" s="4">
+        <v>321</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A25" s="3">
-        <v>238</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="A25" s="4">
+        <v>322</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A26" s="3">
-        <v>239</v>
-      </c>
-      <c r="B26" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="29.25" spans="1:4">
-      <c r="A27" s="3">
-        <v>240</v>
-      </c>
-      <c r="B27" s="3" t="s">
+    <row r="27" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A27" s="4">
+        <v>324</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="29.25" spans="1:4">
+    <row r="28" s="1" customFormat="1" ht="15" spans="1:4">
       <c r="A28" s="3">
-        <v>241</v>
-      </c>
-      <c r="B28" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A29" s="3">
-        <v>242</v>
-      </c>
-      <c r="B29" s="3" t="s">
+      <c r="A29" s="4">
+        <v>326</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A30" s="3">
-        <v>243</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="A30" s="4">
+        <v>327</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="15" spans="1:4">
-      <c r="A31" s="3">
-        <v>244</v>
-      </c>
-      <c r="B31" s="3" t="s">
+    <row r="31" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A31" s="4">
+        <v>328</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A32" s="3">
-        <v>245</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="A32" s="4">
+        <v>329</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="29.25" spans="1:4">
-      <c r="A33" s="3">
-        <v>246</v>
-      </c>
-      <c r="B33" s="3" t="s">
+    <row r="33" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A33" s="4">
+        <v>330</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A34" s="3">
-        <v>247</v>
-      </c>
-      <c r="B34" s="3" t="s">
+    <row r="34" s="1" customFormat="1" ht="29.25" spans="1:4">
+      <c r="A34" s="4">
+        <v>331</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A35" s="3">
-        <v>248</v>
-      </c>
-      <c r="B35" s="3" t="s">
+    <row r="35" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A35" s="4">
+        <v>332</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A36" s="3">
-        <v>249</v>
-      </c>
-      <c r="B36" s="3" t="s">
+      <c r="A36" s="4">
+        <v>333</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="3" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A37" s="3">
-        <v>250</v>
-      </c>
-      <c r="B37" s="3" t="s">
+      <c r="A37" s="4">
+        <v>334</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="3" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A38" s="3">
-        <v>251</v>
-      </c>
-      <c r="B38" s="3" t="s">
+      <c r="A38" s="4">
+        <v>335</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="15" spans="1:4">
+    <row r="39" s="1" customFormat="1" ht="29.25" spans="1:4">
       <c r="A39" s="4">
-        <v>252</v>
-      </c>
-      <c r="B39" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" ht="28.5" spans="1:4">
-      <c r="A40" s="3">
-        <v>253</v>
-      </c>
-      <c r="B40" s="3" t="s">
+    <row r="40" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A40" s="4">
+        <v>337</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="3" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" ht="28.5" spans="1:4">
       <c r="A41" s="3">
-        <v>254</v>
-      </c>
-      <c r="B41" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" ht="14.25" spans="1:4">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="14.25" spans="1:4">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="14.25" spans="1:4">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" ht="14.25" spans="1:4">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
+    <row r="42" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A42" s="4">
+        <v>339</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A43" s="4">
+        <v>340</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A44" s="4">
+        <v>341</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45" ht="15" spans="1:4">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
